--- a/data/trans_orig/IQ3006_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3006_MoAR-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en años en la que empezaron a beber leche normal</t>
+          <t>Menores según la edad en años en la que empezaron a beber leche normal (tasa de respuesta: 32,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,27 +677,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,48; 19,69</t>
+          <t>6,18; 19,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,25; 18,08</t>
+          <t>11,99; 18,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 16,87</t>
+          <t>7,97; 16,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,91; 16,51</t>
+          <t>10,94; 16,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,86; 19,43</t>
+          <t>13,97; 19,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,47; 15,74</t>
+          <t>10,55; 16,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,57; 17,7</t>
+          <t>13,59; 17,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,0; 15,54</t>
+          <t>8,12; 15,25</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,6; 15,23</t>
+          <t>12,38; 15,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,26; 14,6</t>
+          <t>12,21; 14,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,0; 15,15</t>
+          <t>12,1; 15,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,89; 13,22</t>
+          <t>10,79; 13,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,56; 13,93</t>
+          <t>10,63; 13,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,13; 13,98</t>
+          <t>11,11; 14,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,89; 13,73</t>
+          <t>11,94; 13,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,88; 13,85</t>
+          <t>11,92; 13,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,92; 14,1</t>
+          <t>11,89; 13,92</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,36; 15,91</t>
+          <t>9,26; 15,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,22; 16,94</t>
+          <t>12,11; 16,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,18; 16,14</t>
+          <t>10,31; 16,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,73; 15,05</t>
+          <t>10,75; 15,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,29; 17,06</t>
+          <t>12,33; 17,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,36; 16,84</t>
+          <t>10,44; 17,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,85; 14,71</t>
+          <t>11,01; 14,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,78; 16,0</t>
+          <t>12,75; 15,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,93; 15,04</t>
+          <t>10,83; 15,41</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,06; 15,01</t>
+          <t>11,97; 14,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,82; 14,89</t>
+          <t>12,79; 14,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,69; 14,33</t>
+          <t>11,92; 14,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,5; 13,45</t>
+          <t>11,4; 13,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,18; 14,75</t>
+          <t>12,17; 14,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,18; 13,89</t>
+          <t>11,23; 13,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,06; 13,73</t>
+          <t>12,09; 13,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,78; 14,37</t>
+          <t>12,9; 14,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,86; 13,65</t>
+          <t>11,85; 13,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3006_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3006_MoAR-Estudios-trans_orig.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,99; 18,1</t>
+          <t>12,04; 18,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,94; 16,44</t>
+          <t>11,05; 16,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,97; 19,44</t>
+          <t>13,95; 19,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,55; 16,04</t>
+          <t>10,57; 16,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,59; 17,54</t>
+          <t>13,89; 17,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,12; 15,25</t>
+          <t>8,12; 15,07</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,38; 15,37</t>
+          <t>12,45; 15,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,21; 14,7</t>
+          <t>12,37; 14,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,1; 15,15</t>
+          <t>12,04; 14,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,79; 13,17</t>
+          <t>10,82; 13,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,63; 13,85</t>
+          <t>10,62; 13,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,11; 14,12</t>
+          <t>11,07; 14,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,94; 13,82</t>
+          <t>11,91; 13,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,92; 13,87</t>
+          <t>11,99; 13,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,89; 13,92</t>
+          <t>11,84; 13,98</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,26; 15,78</t>
+          <t>9,3; 16,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,11; 16,84</t>
+          <t>12,02; 16,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 16,15</t>
+          <t>10,39; 16,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,75; 15,2</t>
+          <t>10,74; 15,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,33; 17,01</t>
+          <t>12,28; 16,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,44; 17,01</t>
+          <t>10,42; 17,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,01; 14,67</t>
+          <t>10,93; 14,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,75; 15,91</t>
+          <t>12,93; 16,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,83; 15,41</t>
+          <t>10,94; 15,14</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,97; 14,86</t>
+          <t>11,93; 14,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,79; 14,75</t>
+          <t>12,8; 14,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,92; 14,41</t>
+          <t>11,92; 14,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,4; 13,49</t>
+          <t>11,45; 13,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,17; 14,64</t>
+          <t>12,24; 14,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,23; 13,99</t>
+          <t>11,2; 13,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 13,72</t>
+          <t>12,05; 13,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,9; 14,5</t>
+          <t>12,8; 14,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,85; 13,72</t>
+          <t>11,91; 13,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3006_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3006_MoAR-Estudios-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13,01</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16,22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>12,85</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>15,13</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,01</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16,22</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 19,67</t>
+          <t>10,91; 16,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,04; 18,0</t>
+          <t>13,86; 19,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,97; 16,87</t>
+          <t>6,0; 12,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,05; 16,35</t>
+          <t>6,48; 19,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,95; 19,41</t>
+          <t>12,25; 18,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 12,0</t>
+          <t>7,94; 16,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,57; 16,24</t>
+          <t>10,47; 15,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,89; 17,65</t>
+          <t>13,57; 17,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,12; 15,07</t>
+          <t>8,0; 15,54</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12,05</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,41</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12,44</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>13,83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>13,37</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>13,39</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,05</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,41</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,44</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,45; 15,25</t>
+          <t>10,89; 13,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,37; 14,73</t>
+          <t>10,56; 13,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,04; 14,96</t>
+          <t>11,13; 13,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,82; 13,31</t>
+          <t>12,6; 15,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,62; 13,67</t>
+          <t>12,26; 14,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,07; 14,15</t>
+          <t>12,0; 15,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,91; 13,68</t>
+          <t>11,89; 13,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,99; 13,93</t>
+          <t>11,88; 13,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,84; 13,98</t>
+          <t>11,92; 14,1</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,02</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14,62</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13,16</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>12,92</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>13,7</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12,61</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13,02</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,62</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,16</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,3; 16,02</t>
+          <t>10,73; 15,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,02; 16,71</t>
+          <t>12,29; 17,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,39; 16,09</t>
+          <t>10,36; 16,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,74; 15,11</t>
+          <t>9,36; 15,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,28; 16,95</t>
+          <t>12,22; 16,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,42; 17,05</t>
+          <t>10,18; 16,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,93; 14,62</t>
+          <t>10,85; 14,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,93; 16,1</t>
+          <t>12,78; 16,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,94; 15,14</t>
+          <t>10,93; 15,04</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,48</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,51</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>13,47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>13,68</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,48</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,51</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 14,9</t>
+          <t>11,5; 13,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,8; 14,81</t>
+          <t>12,18; 14,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,92; 14,53</t>
+          <t>11,18; 13,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,45; 13,46</t>
+          <t>12,06; 15,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,24; 14,58</t>
+          <t>12,82; 14,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,97</t>
+          <t>11,69; 14,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,05; 13,72</t>
+          <t>12,06; 13,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,8; 14,39</t>
+          <t>12,78; 14,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,91; 13,83</t>
+          <t>11,86; 13,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3006_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3006_MoAR-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en años en la que empezaron a beber leche normal (tasa de respuesta: 32,45%)</t>
+          <t>Edad media en meses a la que los menores empezaron a beber leche normal (tasa de respuesta: 32,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>13,01</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16,22</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,85</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,13</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,25</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,96</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15,64</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11,26</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>13.00629849736902</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>16.21630629088257</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>9.197563091534995</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>12.85419528103794</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>15.12668880995382</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>12.24938595325538</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>12.96040048800702</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>15.63665665408971</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>11.25742557280382</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>10,91; 16,51</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13,86; 19,43</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6,0; 12,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6,48; 19,69</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12,25; 18,08</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,94; 16,87</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,47; 15,74</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13,57; 17,7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8,0; 15,54</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>10.91402681084938</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>13.86194462632438</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>6.475820392161293</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>12.25208249276584</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>7.937272583281792</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>10.46722602049116</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>13.5679196419738</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>8.000296010086767</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>16.50750492911726</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>19.42648992884159</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>19.694278444955</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>18.0824590205021</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>16.86778950260562</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>15.73870492159114</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>17.70343251212173</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>15.54144568800127</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>12,05</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12,41</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12,44</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13,83</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,37</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,39</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,83</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12,92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12,87</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>10,89; 13,22</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10,56; 13,93</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11,13; 13,98</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12,6; 15,23</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12,26; 14,6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,0; 15,15</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,89; 13,73</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11,88; 13,85</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11,92; 14,1</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>12.04655104377711</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>12.40672940324278</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>12.43964988506161</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>13.83170512837862</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>13.3728960240458</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>13.39391167761644</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>12.8319474108835</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>12.92087627297029</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>12.86976787787359</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>13,02</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14,62</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13,16</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,92</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,7</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,61</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,98</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14,15</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>12,9</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>10.88710744438125</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>10.56038450888728</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>11.12654187896183</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>12.59564095366357</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>12.26151828898131</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>12.00145609906722</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>11.89409414720736</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>11.88221802705683</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>11.91896286893123</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>10,73; 15,05</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12,29; 17,06</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10,36; 16,84</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9,36; 15,91</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>12,22; 16,94</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>10,18; 16,14</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,85; 14,71</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>12,78; 16,0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>10,93; 15,04</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>13.22463256053934</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>13.92686533812807</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>13.98337853036023</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>15.23133755592174</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>14.60059257697147</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>15.15004130632737</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>13.73494312746402</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>13.84890831953209</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>14.09865608003964</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,107 +845,215 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>12,48</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>13,5</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12,51</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,47</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,68</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,89</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13,6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12,79</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>13.01924717931104</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>14.61655994364553</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>13.15579536291919</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>12.92251306638035</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>13.7012062944448</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>12.61424220992316</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>12.97877432971751</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>14.14962858515213</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>12.89748890222682</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>11,5; 13,45</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>12,18; 14,75</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11,18; 13,89</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12,06; 15,01</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12,82; 14,89</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11,69; 14,33</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,06; 13,73</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>12,78; 14,37</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>11,86; 13,65</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>10.72887862574428</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>12.29185797740285</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>10.35959188781971</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>9.357718714865298</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>12.21847801891093</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>10.18275404179297</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>10.85083921069168</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>12.77820986404909</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>10.92735578904442</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>15.04774314941468</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>17.06086058098912</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>16.84368724513497</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>15.91203425520251</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>16.93564661688464</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>16.13585760662689</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>14.7097920915633</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>15.99810881938713</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>15.03959722446868</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>12.47940148167789</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>13.49924036577606</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>12.50837994312027</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>13.46861685162289</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>13.68314837747166</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>13.09862053076608</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>12.89211955043876</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>13.59600984365392</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>12.78585706280553</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>11.50193427217702</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>12.18039721621262</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>11.18194501399569</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>12.06133895234819</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>12.81889711434753</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>11.69357633633587</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>12.06281986747988</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>12.77502136732149</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>11.85601471548406</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>13.45410959575876</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>14.74564290196101</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>13.88503730545816</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>15.0127250221112</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>14.8948749878188</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>14.32679585078538</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>13.73021332953642</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>14.37143749666116</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>13.65093586345517</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1061,13 +1062,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
